--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C3A7CFD-8761-4C67-9C95-22018640D430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10E6D33E-1B9B-4A3D-A5BA-E7F6C3A4B52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{400A94E0-7051-4705-94B0-EA792A3514D1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{63E4AE33-48FE-471D-AFB6-085FE2308E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD9F47C-1E98-4C86-8546-B96D2C030C0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D034BFB-96AC-4ED7-9DFC-5F8DAA1D8D8A}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EBA626E-E2B8-4E58-A56B-B7E279AC1918}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D26DE1-2169-4A04-9913-17C6765203E0}">
   <dimension ref="B9:X160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15652,7 +15652,7 @@
         <v>0.5</v>
       </c>
       <c r="M11">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N11">
         <v>50</v>
@@ -22072,7 +22072,7 @@
         <v>0.5</v>
       </c>
       <c r="M119">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N119">
         <v>50</v>
@@ -23606,7 +23606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D420D8-16E1-4712-A4BB-1BE4AC7AF4D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EDD6E73-015A-4871-B538-DC492AC4EC15}">
   <dimension ref="B9:X400"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23898,7 +23898,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M14">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N14">
         <v>50</v>
@@ -23963,7 +23963,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M15">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N15">
         <v>50</v>
@@ -24028,7 +24028,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M16">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N16">
         <v>77</v>
@@ -24093,7 +24093,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M17">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N17">
         <v>102</v>
@@ -24217,7 +24217,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M19">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N19">
         <v>72</v>
@@ -24282,7 +24282,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M20">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N20">
         <v>50</v>
@@ -24347,7 +24347,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M21">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N21">
         <v>50</v>
@@ -24412,7 +24412,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M22">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N22">
         <v>50</v>
@@ -24477,7 +24477,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M23">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N23">
         <v>50</v>
@@ -24601,7 +24601,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M25">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N25">
         <v>50</v>
@@ -24843,7 +24843,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M29">
-        <v>-0.14000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N29">
         <v>50</v>
@@ -25144,7 +25144,7 @@
         <v>1.2</v>
       </c>
       <c r="M34">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N34">
         <v>80</v>
@@ -25209,7 +25209,7 @@
         <v>1.2</v>
       </c>
       <c r="M35">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N35">
         <v>47</v>
@@ -25274,7 +25274,7 @@
         <v>1.2</v>
       </c>
       <c r="M36">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N36">
         <v>47</v>
@@ -25339,7 +25339,7 @@
         <v>1.2</v>
       </c>
       <c r="M37">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N37">
         <v>47</v>
@@ -25404,7 +25404,7 @@
         <v>1.2</v>
       </c>
       <c r="M38">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N38">
         <v>47</v>
@@ -25469,7 +25469,7 @@
         <v>1.2</v>
       </c>
       <c r="M39">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N39">
         <v>47</v>
@@ -25534,7 +25534,7 @@
         <v>1.2</v>
       </c>
       <c r="M40">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N40">
         <v>48</v>
@@ -25599,7 +25599,7 @@
         <v>1.2</v>
       </c>
       <c r="M41">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N41">
         <v>47</v>
@@ -25664,7 +25664,7 @@
         <v>1.2</v>
       </c>
       <c r="M42">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N42">
         <v>48</v>
@@ -25729,7 +25729,7 @@
         <v>1.2</v>
       </c>
       <c r="M43">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N43">
         <v>48</v>
@@ -25794,7 +25794,7 @@
         <v>1.2</v>
       </c>
       <c r="M44">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N44">
         <v>48</v>
@@ -25859,7 +25859,7 @@
         <v>1.2</v>
       </c>
       <c r="M45">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N45">
         <v>48</v>
@@ -25924,7 +25924,7 @@
         <v>1.2</v>
       </c>
       <c r="M46">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N46">
         <v>74</v>
@@ -25989,7 +25989,7 @@
         <v>1.2</v>
       </c>
       <c r="M47">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N47">
         <v>64</v>
@@ -26054,7 +26054,7 @@
         <v>1.2</v>
       </c>
       <c r="M48">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N48">
         <v>58</v>
@@ -26119,7 +26119,7 @@
         <v>1.2</v>
       </c>
       <c r="M49">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N49">
         <v>50</v>
@@ -26184,7 +26184,7 @@
         <v>1.2</v>
       </c>
       <c r="M50">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N50">
         <v>54</v>
@@ -26249,7 +26249,7 @@
         <v>1.2</v>
       </c>
       <c r="M51">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N51">
         <v>54</v>
@@ -26314,7 +26314,7 @@
         <v>1.2</v>
       </c>
       <c r="M52">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N52">
         <v>54</v>
@@ -26379,7 +26379,7 @@
         <v>1.2</v>
       </c>
       <c r="M53">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N53">
         <v>52</v>
@@ -26444,7 +26444,7 @@
         <v>1.2</v>
       </c>
       <c r="M54">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N54">
         <v>52</v>
@@ -26509,7 +26509,7 @@
         <v>1.2</v>
       </c>
       <c r="M55">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N55">
         <v>17</v>
@@ -26810,7 +26810,7 @@
         <v>1.2</v>
       </c>
       <c r="M60">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N60">
         <v>57</v>
@@ -26875,7 +26875,7 @@
         <v>1.2</v>
       </c>
       <c r="M61">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N61">
         <v>52</v>
@@ -26940,7 +26940,7 @@
         <v>1.2</v>
       </c>
       <c r="M62">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N62">
         <v>46</v>
@@ -27005,7 +27005,7 @@
         <v>1.2</v>
       </c>
       <c r="M63">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N63">
         <v>36</v>
@@ -27070,7 +27070,7 @@
         <v>1.2</v>
       </c>
       <c r="M64">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N64">
         <v>44</v>
@@ -27135,7 +27135,7 @@
         <v>1.2</v>
       </c>
       <c r="M65">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N65">
         <v>40</v>
@@ -27200,7 +27200,7 @@
         <v>1.2</v>
       </c>
       <c r="M66">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N66">
         <v>52</v>
@@ -27265,7 +27265,7 @@
         <v>1.2</v>
       </c>
       <c r="M67">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N67">
         <v>47</v>
@@ -27330,7 +27330,7 @@
         <v>1.2</v>
       </c>
       <c r="M68">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N68">
         <v>30</v>
@@ -27395,7 +27395,7 @@
         <v>1.2</v>
       </c>
       <c r="M69">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N69">
         <v>30</v>
@@ -27460,7 +27460,7 @@
         <v>1.2</v>
       </c>
       <c r="M70">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N70">
         <v>58</v>
@@ -27525,7 +27525,7 @@
         <v>1.2</v>
       </c>
       <c r="M71">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N71">
         <v>58</v>
@@ -27590,7 +27590,7 @@
         <v>1.2</v>
       </c>
       <c r="M72">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N72">
         <v>58</v>
@@ -27655,7 +27655,7 @@
         <v>1.2</v>
       </c>
       <c r="M73">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N73">
         <v>58</v>
@@ -27720,7 +27720,7 @@
         <v>1.2</v>
       </c>
       <c r="M74">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N74">
         <v>57</v>
@@ -27785,7 +27785,7 @@
         <v>1.2</v>
       </c>
       <c r="M75">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N75">
         <v>57</v>
@@ -27850,7 +27850,7 @@
         <v>1.2</v>
       </c>
       <c r="M76">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N76">
         <v>56</v>
@@ -27915,7 +27915,7 @@
         <v>1.2</v>
       </c>
       <c r="M77">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N77">
         <v>64</v>
@@ -28570,7 +28570,7 @@
         <v>1.2</v>
       </c>
       <c r="M88">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N88">
         <v>60</v>
@@ -28635,7 +28635,7 @@
         <v>1.2</v>
       </c>
       <c r="M89">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N89">
         <v>52</v>
@@ -28700,7 +28700,7 @@
         <v>1.2</v>
       </c>
       <c r="M90">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N90">
         <v>45</v>
@@ -29001,7 +29001,7 @@
         <v>1.2</v>
       </c>
       <c r="M95">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N95">
         <v>62</v>
@@ -29066,7 +29066,7 @@
         <v>1.2</v>
       </c>
       <c r="M96">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N96">
         <v>62</v>
@@ -29131,7 +29131,7 @@
         <v>1.2</v>
       </c>
       <c r="M97">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N97">
         <v>62</v>
@@ -29196,7 +29196,7 @@
         <v>1.2</v>
       </c>
       <c r="M98">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N98">
         <v>62</v>
@@ -29261,7 +29261,7 @@
         <v>1.2</v>
       </c>
       <c r="M99">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N99">
         <v>53</v>
@@ -29326,7 +29326,7 @@
         <v>1.2</v>
       </c>
       <c r="M100">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N100">
         <v>52</v>
@@ -29391,7 +29391,7 @@
         <v>1.2</v>
       </c>
       <c r="M101">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N101">
         <v>38</v>
@@ -29692,7 +29692,7 @@
         <v>1.2</v>
       </c>
       <c r="M106">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N106">
         <v>97</v>
@@ -29875,7 +29875,7 @@
         <v>1.2</v>
       </c>
       <c r="M109">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N109">
         <v>83</v>
@@ -30117,7 +30117,7 @@
         <v>1.2</v>
       </c>
       <c r="M113">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N113">
         <v>76</v>
@@ -30182,7 +30182,7 @@
         <v>1.2</v>
       </c>
       <c r="M114">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N114">
         <v>76</v>
@@ -30247,7 +30247,7 @@
         <v>1.2</v>
       </c>
       <c r="M115">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N115">
         <v>76</v>
@@ -30312,7 +30312,7 @@
         <v>1.2</v>
       </c>
       <c r="M116">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N116">
         <v>76</v>
@@ -30377,7 +30377,7 @@
         <v>1.2</v>
       </c>
       <c r="M117">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N117">
         <v>73</v>
@@ -30442,7 +30442,7 @@
         <v>1.2</v>
       </c>
       <c r="M118">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N118">
         <v>73</v>
@@ -30507,7 +30507,7 @@
         <v>1.2</v>
       </c>
       <c r="M119">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N119">
         <v>72</v>
@@ -30572,7 +30572,7 @@
         <v>1.2</v>
       </c>
       <c r="M120">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N120">
         <v>69</v>
@@ -30637,7 +30637,7 @@
         <v>1.2</v>
       </c>
       <c r="M121">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N121">
         <v>69</v>
@@ -30702,7 +30702,7 @@
         <v>1.2</v>
       </c>
       <c r="M122">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N122">
         <v>45</v>
@@ -30767,7 +30767,7 @@
         <v>1.2</v>
       </c>
       <c r="M123">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N123">
         <v>39</v>
@@ -30832,7 +30832,7 @@
         <v>1.2</v>
       </c>
       <c r="M124">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N124">
         <v>32</v>
@@ -30897,7 +30897,7 @@
         <v>1.2</v>
       </c>
       <c r="M125">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N125">
         <v>90</v>
@@ -30962,7 +30962,7 @@
         <v>1.2</v>
       </c>
       <c r="M126">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N126">
         <v>90</v>
@@ -31027,7 +31027,7 @@
         <v>1.2</v>
       </c>
       <c r="M127">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N127">
         <v>85</v>
@@ -31210,7 +31210,7 @@
         <v>1.2</v>
       </c>
       <c r="M130">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N130">
         <v>48</v>
@@ -31275,7 +31275,7 @@
         <v>1.2</v>
       </c>
       <c r="M131">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N131">
         <v>48</v>
@@ -31340,7 +31340,7 @@
         <v>1.2</v>
       </c>
       <c r="M132">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N132">
         <v>49</v>
@@ -31405,7 +31405,7 @@
         <v>1.2</v>
       </c>
       <c r="M133">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N133">
         <v>49</v>
@@ -31470,7 +31470,7 @@
         <v>1.2</v>
       </c>
       <c r="M134">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N134">
         <v>70</v>
@@ -31535,7 +31535,7 @@
         <v>1.2</v>
       </c>
       <c r="M135">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N135">
         <v>70</v>
@@ -31600,7 +31600,7 @@
         <v>1.2</v>
       </c>
       <c r="M136">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N136">
         <v>70</v>
@@ -31665,7 +31665,7 @@
         <v>1.2</v>
       </c>
       <c r="M137">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N137">
         <v>74</v>
@@ -31730,7 +31730,7 @@
         <v>1.2</v>
       </c>
       <c r="M138">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N138">
         <v>60</v>
@@ -31795,7 +31795,7 @@
         <v>1.2</v>
       </c>
       <c r="M139">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N139">
         <v>60</v>
@@ -31860,7 +31860,7 @@
         <v>1.2</v>
       </c>
       <c r="M140">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N140">
         <v>60</v>
@@ -31925,7 +31925,7 @@
         <v>1.2</v>
       </c>
       <c r="M141">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N141">
         <v>26</v>
@@ -31990,7 +31990,7 @@
         <v>1.2</v>
       </c>
       <c r="M142">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N142">
         <v>26</v>
@@ -32055,7 +32055,7 @@
         <v>1.2</v>
       </c>
       <c r="M143">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N143">
         <v>94</v>
@@ -32120,7 +32120,7 @@
         <v>1.2</v>
       </c>
       <c r="M144">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N144">
         <v>94</v>
@@ -32185,7 +32185,7 @@
         <v>1.2</v>
       </c>
       <c r="M145">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N145">
         <v>94</v>
@@ -32250,7 +32250,7 @@
         <v>1.2</v>
       </c>
       <c r="M146">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N146">
         <v>63</v>
@@ -32315,7 +32315,7 @@
         <v>1.2</v>
       </c>
       <c r="M147">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N147">
         <v>81</v>
@@ -32380,7 +32380,7 @@
         <v>1.2</v>
       </c>
       <c r="M148">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N148">
         <v>50</v>
@@ -32445,7 +32445,7 @@
         <v>1.2</v>
       </c>
       <c r="M149">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N149">
         <v>93</v>
@@ -32510,7 +32510,7 @@
         <v>1.2</v>
       </c>
       <c r="M150">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N150">
         <v>93</v>
@@ -32575,7 +32575,7 @@
         <v>1.2</v>
       </c>
       <c r="M151">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N151">
         <v>92</v>
@@ -32640,7 +32640,7 @@
         <v>1.2</v>
       </c>
       <c r="M152">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N152">
         <v>92</v>
@@ -32705,7 +32705,7 @@
         <v>1.2</v>
       </c>
       <c r="M153">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N153">
         <v>91</v>
@@ -32770,7 +32770,7 @@
         <v>1.2</v>
       </c>
       <c r="M154">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N154">
         <v>91</v>
@@ -32835,7 +32835,7 @@
         <v>1.2</v>
       </c>
       <c r="M155">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N155">
         <v>50</v>
@@ -32900,7 +32900,7 @@
         <v>1.2</v>
       </c>
       <c r="M156">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N156">
         <v>85</v>
@@ -32965,7 +32965,7 @@
         <v>1.2</v>
       </c>
       <c r="M157">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N157">
         <v>75</v>
@@ -33030,7 +33030,7 @@
         <v>1.2</v>
       </c>
       <c r="M158">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N158">
         <v>70</v>
@@ -33095,7 +33095,7 @@
         <v>1.2</v>
       </c>
       <c r="M159">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N159">
         <v>9</v>
@@ -33160,7 +33160,7 @@
         <v>1.2</v>
       </c>
       <c r="M160">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N160">
         <v>70</v>
@@ -33225,7 +33225,7 @@
         <v>1.2</v>
       </c>
       <c r="M161">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N161">
         <v>26</v>
@@ -33290,7 +33290,7 @@
         <v>1.2</v>
       </c>
       <c r="M162">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N162">
         <v>81</v>
@@ -33355,7 +33355,7 @@
         <v>1.2</v>
       </c>
       <c r="M163">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N163">
         <v>63</v>
@@ -33420,7 +33420,7 @@
         <v>1.2</v>
       </c>
       <c r="M164">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N164">
         <v>50</v>
@@ -33485,7 +33485,7 @@
         <v>1.2</v>
       </c>
       <c r="M165">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N165">
         <v>98</v>
@@ -33550,7 +33550,7 @@
         <v>1.2</v>
       </c>
       <c r="M166">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N166">
         <v>59</v>
@@ -33615,7 +33615,7 @@
         <v>1.2</v>
       </c>
       <c r="M167">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N167">
         <v>60</v>
@@ -33680,7 +33680,7 @@
         <v>1.2</v>
       </c>
       <c r="M168">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N168">
         <v>50</v>
@@ -33745,7 +33745,7 @@
         <v>1.2</v>
       </c>
       <c r="M169">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N169">
         <v>50</v>
@@ -33869,7 +33869,7 @@
         <v>1.2</v>
       </c>
       <c r="M171">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N171">
         <v>15</v>
@@ -33934,7 +33934,7 @@
         <v>1.2</v>
       </c>
       <c r="M172">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N172">
         <v>21</v>
@@ -34294,7 +34294,7 @@
         <v>0.5</v>
       </c>
       <c r="M178">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N178">
         <v>31</v>
@@ -34359,7 +34359,7 @@
         <v>0.5</v>
       </c>
       <c r="M179">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N179">
         <v>50</v>
@@ -34424,7 +34424,7 @@
         <v>0.5</v>
       </c>
       <c r="M180">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N180">
         <v>50</v>
@@ -34489,7 +34489,7 @@
         <v>0.5</v>
       </c>
       <c r="M181">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N181">
         <v>52</v>
@@ -34554,7 +34554,7 @@
         <v>0.5</v>
       </c>
       <c r="M182">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N182">
         <v>50</v>
@@ -34619,7 +34619,7 @@
         <v>0.5</v>
       </c>
       <c r="M183">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N183">
         <v>53</v>
@@ -34684,7 +34684,7 @@
         <v>0.5</v>
       </c>
       <c r="M184">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N184">
         <v>50</v>
@@ -34749,7 +34749,7 @@
         <v>0.5</v>
       </c>
       <c r="M185">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N185">
         <v>51</v>
@@ -34814,7 +34814,7 @@
         <v>0.5</v>
       </c>
       <c r="M186">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N186">
         <v>55</v>
@@ -34879,7 +34879,7 @@
         <v>0.5</v>
       </c>
       <c r="M187">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N187">
         <v>50</v>
@@ -34944,7 +34944,7 @@
         <v>0.5</v>
       </c>
       <c r="M188">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N188">
         <v>31</v>
@@ -35068,7 +35068,7 @@
         <v>0.5</v>
       </c>
       <c r="M190">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N190">
         <v>50</v>
@@ -35133,7 +35133,7 @@
         <v>0.5</v>
       </c>
       <c r="M191">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N191">
         <v>50</v>
@@ -35257,7 +35257,7 @@
         <v>0.5</v>
       </c>
       <c r="M193">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N193">
         <v>50</v>
@@ -35322,7 +35322,7 @@
         <v>0.5</v>
       </c>
       <c r="M194">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N194">
         <v>50</v>
@@ -35446,7 +35446,7 @@
         <v>0.5</v>
       </c>
       <c r="M196">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N196">
         <v>50</v>
@@ -35511,7 +35511,7 @@
         <v>0.5</v>
       </c>
       <c r="M197">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N197">
         <v>50</v>
@@ -35576,7 +35576,7 @@
         <v>0.5</v>
       </c>
       <c r="M198">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N198">
         <v>50</v>
@@ -35641,7 +35641,7 @@
         <v>0.5</v>
       </c>
       <c r="M199">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N199">
         <v>50</v>
@@ -36447,7 +36447,7 @@
         <v>1</v>
       </c>
       <c r="M212">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N212">
         <v>50</v>
@@ -36512,7 +36512,7 @@
         <v>1</v>
       </c>
       <c r="M213">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N213">
         <v>50</v>
@@ -36577,7 +36577,7 @@
         <v>1</v>
       </c>
       <c r="M214">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N214">
         <v>100</v>
@@ -36642,7 +36642,7 @@
         <v>1</v>
       </c>
       <c r="M215">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N215">
         <v>97</v>
@@ -36707,7 +36707,7 @@
         <v>1</v>
       </c>
       <c r="M216">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="N216">
         <v>95</v>
@@ -37567,7 +37567,7 @@
         <v>33</v>
       </c>
       <c r="O232">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="Q232" t="s">
         <v>390</v>
@@ -37620,7 +37620,7 @@
         <v>33</v>
       </c>
       <c r="O233">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="Q233" t="s">
         <v>390</v>
@@ -37673,7 +37673,7 @@
         <v>33</v>
       </c>
       <c r="O234">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="Q234" t="s">
         <v>390</v>
@@ -38491,7 +38491,7 @@
         <v>16</v>
       </c>
       <c r="T247" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U247" t="s">
         <v>392</v>
@@ -38553,7 +38553,7 @@
         <v>16</v>
       </c>
       <c r="T248" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U248" t="s">
         <v>392</v>
@@ -39793,7 +39793,7 @@
         <v>16</v>
       </c>
       <c r="T268" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U268" t="s">
         <v>392</v>
@@ -39855,7 +39855,7 @@
         <v>16</v>
       </c>
       <c r="T269" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U269" t="s">
         <v>392</v>
@@ -39979,7 +39979,7 @@
         <v>16</v>
       </c>
       <c r="T271" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U271" t="s">
         <v>392</v>
@@ -40041,7 +40041,7 @@
         <v>16</v>
       </c>
       <c r="T272" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U272" t="s">
         <v>392</v>
@@ -40723,7 +40723,7 @@
         <v>16</v>
       </c>
       <c r="T283" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U283" t="s">
         <v>392</v>
@@ -40785,7 +40785,7 @@
         <v>16</v>
       </c>
       <c r="T284" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U284" t="s">
         <v>392</v>
@@ -45235,7 +45235,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA8F1470-C701-4755-A3FE-D3A0B32745AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A6D3DAD-67E1-470A-A890-719D4F1D4DB6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10E6D33E-1B9B-4A3D-A5BA-E7F6C3A4B52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{755ABFD3-3E31-446D-8CF3-476E4F230B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{63E4AE33-48FE-471D-AFB6-085FE2308E7C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4AB4A6BD-F296-4473-9EB9-224FB3CFAB25}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D034BFB-96AC-4ED7-9DFC-5F8DAA1D8D8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B37E894-BA6E-406D-915D-7115B5055845}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D26DE1-2169-4A04-9913-17C6765203E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39641002-EF09-4AE9-82DA-5548EF207CA7}">
   <dimension ref="B9:X160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23606,7 +23606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EDD6E73-015A-4871-B538-DC492AC4EC15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F398D148-15CC-4112-B02B-50667ED3AD5C}">
   <dimension ref="B9:X400"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38491,7 +38491,7 @@
         <v>16</v>
       </c>
       <c r="T247" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U247" t="s">
         <v>392</v>
@@ -38553,7 +38553,7 @@
         <v>16</v>
       </c>
       <c r="T248" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U248" t="s">
         <v>392</v>
@@ -38615,7 +38615,7 @@
         <v>16</v>
       </c>
       <c r="T249" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U249" t="s">
         <v>392</v>
@@ -38677,7 +38677,7 @@
         <v>16</v>
       </c>
       <c r="T250" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U250" t="s">
         <v>392</v>
@@ -38863,7 +38863,7 @@
         <v>16</v>
       </c>
       <c r="T253" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U253" t="s">
         <v>392</v>
@@ -38925,7 +38925,7 @@
         <v>16</v>
       </c>
       <c r="T254" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U254" t="s">
         <v>392</v>
@@ -39793,7 +39793,7 @@
         <v>16</v>
       </c>
       <c r="T268" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U268" t="s">
         <v>392</v>
@@ -39855,7 +39855,7 @@
         <v>16</v>
       </c>
       <c r="T269" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U269" t="s">
         <v>392</v>
@@ -39979,7 +39979,7 @@
         <v>16</v>
       </c>
       <c r="T271" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U271" t="s">
         <v>392</v>
@@ -40041,7 +40041,7 @@
         <v>16</v>
       </c>
       <c r="T272" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U272" t="s">
         <v>392</v>
@@ -40847,7 +40847,7 @@
         <v>16</v>
       </c>
       <c r="T285" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U285" t="s">
         <v>392</v>
@@ -40909,7 +40909,7 @@
         <v>16</v>
       </c>
       <c r="T286" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U286" t="s">
         <v>392</v>
@@ -41026,7 +41026,7 @@
         <v>33</v>
       </c>
       <c r="O289">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="290" spans="2:15" x14ac:dyDescent="0.45">
@@ -41055,7 +41055,7 @@
         <v>33</v>
       </c>
       <c r="O290">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="291" spans="2:15" x14ac:dyDescent="0.45">
@@ -41084,7 +41084,7 @@
         <v>33</v>
       </c>
       <c r="O291">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="292" spans="2:15" x14ac:dyDescent="0.45">
@@ -45235,7 +45235,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A6D3DAD-67E1-470A-A890-719D4F1D4DB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33AAE676-8FD7-47D2-BFB2-334E3D432B7A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{755ABFD3-3E31-446D-8CF3-476E4F230B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C3A111F-BD68-419A-83BA-01A180321F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4AB4A6BD-F296-4473-9EB9-224FB3CFAB25}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{307EBA34-6A8D-4963-A3BB-EE42C6130AA6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B37E894-BA6E-406D-915D-7115B5055845}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9425D7D8-9365-4780-A3FF-95B045860E09}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39641002-EF09-4AE9-82DA-5548EF207CA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D90B996-AC3C-4C55-8FAA-38C57AC19038}">
   <dimension ref="B9:X160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23606,7 +23606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F398D148-15CC-4112-B02B-50667ED3AD5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3253ADF-663C-4FCF-ABBD-2E9C5220D37F}">
   <dimension ref="B9:X400"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37567,7 +37567,7 @@
         <v>33</v>
       </c>
       <c r="O232">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017352</v>
       </c>
       <c r="Q232" t="s">
         <v>390</v>
@@ -37620,7 +37620,7 @@
         <v>33</v>
       </c>
       <c r="O233">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017352</v>
       </c>
       <c r="Q233" t="s">
         <v>390</v>
@@ -37673,7 +37673,7 @@
         <v>33</v>
       </c>
       <c r="O234">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017352</v>
       </c>
       <c r="Q234" t="s">
         <v>390</v>
@@ -37809,7 +37809,7 @@
         <v>16</v>
       </c>
       <c r="T236" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U236" t="s">
         <v>392</v>
@@ -37871,7 +37871,7 @@
         <v>16</v>
       </c>
       <c r="T237" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U237" t="s">
         <v>392</v>
@@ -37933,7 +37933,7 @@
         <v>16</v>
       </c>
       <c r="T238" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U238" t="s">
         <v>392</v>
@@ -37995,7 +37995,7 @@
         <v>16</v>
       </c>
       <c r="T239" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U239" t="s">
         <v>392</v>
@@ -38491,7 +38491,7 @@
         <v>16</v>
       </c>
       <c r="T247" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U247" t="s">
         <v>392</v>
@@ -38553,7 +38553,7 @@
         <v>16</v>
       </c>
       <c r="T248" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U248" t="s">
         <v>392</v>
@@ -38863,7 +38863,7 @@
         <v>16</v>
       </c>
       <c r="T253" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U253" t="s">
         <v>392</v>
@@ -38925,7 +38925,7 @@
         <v>16</v>
       </c>
       <c r="T254" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U254" t="s">
         <v>392</v>
@@ -39793,7 +39793,7 @@
         <v>16</v>
       </c>
       <c r="T268" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U268" t="s">
         <v>392</v>
@@ -39855,7 +39855,7 @@
         <v>16</v>
       </c>
       <c r="T269" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U269" t="s">
         <v>392</v>
@@ -39979,7 +39979,7 @@
         <v>16</v>
       </c>
       <c r="T271" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U271" t="s">
         <v>392</v>
@@ -40041,7 +40041,7 @@
         <v>16</v>
       </c>
       <c r="T272" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U272" t="s">
         <v>392</v>
@@ -40723,7 +40723,7 @@
         <v>16</v>
       </c>
       <c r="T283" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U283" t="s">
         <v>392</v>
@@ -40785,7 +40785,7 @@
         <v>16</v>
       </c>
       <c r="T284" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U284" t="s">
         <v>392</v>
@@ -40847,7 +40847,7 @@
         <v>16</v>
       </c>
       <c r="T285" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U285" t="s">
         <v>392</v>
@@ -40909,7 +40909,7 @@
         <v>16</v>
       </c>
       <c r="T286" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U286" t="s">
         <v>392</v>
@@ -41026,7 +41026,7 @@
         <v>33</v>
       </c>
       <c r="O289">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="290" spans="2:15" x14ac:dyDescent="0.45">
@@ -41055,7 +41055,7 @@
         <v>33</v>
       </c>
       <c r="O290">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="291" spans="2:15" x14ac:dyDescent="0.45">
@@ -41084,7 +41084,7 @@
         <v>33</v>
       </c>
       <c r="O291">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="292" spans="2:15" x14ac:dyDescent="0.45">
@@ -45235,7 +45235,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33AAE676-8FD7-47D2-BFB2-334E3D432B7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B5676E2-9FDF-4CAF-92C8-6DB428ABB60A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C3A111F-BD68-419A-83BA-01A180321F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF102528-07B4-48D6-BA39-0DE0721E550C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{307EBA34-6A8D-4963-A3BB-EE42C6130AA6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{63992410-171E-482D-97D4-0D0FA385B559}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9425D7D8-9365-4780-A3FF-95B045860E09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{634BA8C3-AE9A-4B06-ADB8-D92E626F789B}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D90B996-AC3C-4C55-8FAA-38C57AC19038}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B59312-91D7-4DC6-920C-0524F2A33D52}">
   <dimension ref="B9:X160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23606,7 +23606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3253ADF-663C-4FCF-ABBD-2E9C5220D37F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC244030-51E9-456E-853D-791D8134B9AF}">
   <dimension ref="B9:X400"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37567,7 +37567,7 @@
         <v>33</v>
       </c>
       <c r="O232">
-        <v>0.13941713559017352</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="Q232" t="s">
         <v>390</v>
@@ -37620,7 +37620,7 @@
         <v>33</v>
       </c>
       <c r="O233">
-        <v>0.13941713559017352</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="Q233" t="s">
         <v>390</v>
@@ -37673,7 +37673,7 @@
         <v>33</v>
       </c>
       <c r="O234">
-        <v>0.13941713559017352</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="Q234" t="s">
         <v>390</v>
@@ -37933,7 +37933,7 @@
         <v>16</v>
       </c>
       <c r="T238" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U238" t="s">
         <v>392</v>
@@ -37995,7 +37995,7 @@
         <v>16</v>
       </c>
       <c r="T239" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U239" t="s">
         <v>392</v>
@@ -38615,7 +38615,7 @@
         <v>16</v>
       </c>
       <c r="T249" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U249" t="s">
         <v>392</v>
@@ -38677,7 +38677,7 @@
         <v>16</v>
       </c>
       <c r="T250" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U250" t="s">
         <v>392</v>
@@ -39793,7 +39793,7 @@
         <v>16</v>
       </c>
       <c r="T268" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U268" t="s">
         <v>392</v>
@@ -39855,7 +39855,7 @@
         <v>16</v>
       </c>
       <c r="T269" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U269" t="s">
         <v>392</v>
@@ -45235,7 +45235,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B5676E2-9FDF-4CAF-92C8-6DB428ABB60A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC88AE48-1165-48A6-A076-DF8860B70097}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF102528-07B4-48D6-BA39-0DE0721E550C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C6BCC54-2635-4467-94A5-3AF1BA52FD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{63992410-171E-482D-97D4-0D0FA385B559}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0C89D258-2E3B-4941-85D4-0AA166755B5A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{634BA8C3-AE9A-4B06-ADB8-D92E626F789B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1A4315-5F80-4A33-AC04-B2CB1684092D}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B59312-91D7-4DC6-920C-0524F2A33D52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B84AD6-E117-43A0-A057-63AE051A2F63}">
   <dimension ref="B9:X160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23606,7 +23606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC244030-51E9-456E-853D-791D8134B9AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B9F41D-CE4C-47BA-ACDC-82F793DD23D9}">
   <dimension ref="B9:X400"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37567,7 +37567,7 @@
         <v>33</v>
       </c>
       <c r="O232">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="Q232" t="s">
         <v>390</v>
@@ -37620,7 +37620,7 @@
         <v>33</v>
       </c>
       <c r="O233">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="Q233" t="s">
         <v>390</v>
@@ -37673,7 +37673,7 @@
         <v>33</v>
       </c>
       <c r="O234">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="Q234" t="s">
         <v>390</v>
@@ -37933,7 +37933,7 @@
         <v>16</v>
       </c>
       <c r="T238" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U238" t="s">
         <v>392</v>
@@ -37995,7 +37995,7 @@
         <v>16</v>
       </c>
       <c r="T239" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U239" t="s">
         <v>392</v>
@@ -38491,7 +38491,7 @@
         <v>16</v>
       </c>
       <c r="T247" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U247" t="s">
         <v>392</v>
@@ -38553,7 +38553,7 @@
         <v>16</v>
       </c>
       <c r="T248" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U248" t="s">
         <v>392</v>
@@ -39793,7 +39793,7 @@
         <v>16</v>
       </c>
       <c r="T268" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U268" t="s">
         <v>392</v>
@@ -39855,7 +39855,7 @@
         <v>16</v>
       </c>
       <c r="T269" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U269" t="s">
         <v>392</v>
@@ -39979,7 +39979,7 @@
         <v>16</v>
       </c>
       <c r="T271" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U271" t="s">
         <v>392</v>
@@ -40041,7 +40041,7 @@
         <v>16</v>
       </c>
       <c r="T272" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U272" t="s">
         <v>392</v>
@@ -45235,7 +45235,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC88AE48-1165-48A6-A076-DF8860B70097}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7E8BAB-84D9-4B6D-97E3-A907256700EC}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C6BCC54-2635-4467-94A5-3AF1BA52FD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA2B285B-0F18-4629-BA3B-CD1AC42B9145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0C89D258-2E3B-4941-85D4-0AA166755B5A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FCAA7BD2-B2A9-45D3-8050-D4A5096067F9}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1A4315-5F80-4A33-AC04-B2CB1684092D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB5EC7F-6BEE-40FD-B59C-532F02F00370}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B84AD6-E117-43A0-A057-63AE051A2F63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{379F4016-F685-4717-866A-4E79EF8981AC}">
   <dimension ref="B9:X160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23606,7 +23606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B9F41D-CE4C-47BA-ACDC-82F793DD23D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{215FB4D1-BAB0-45C2-B67F-5EA690E6933C}">
   <dimension ref="B9:X400"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37809,7 +37809,7 @@
         <v>16</v>
       </c>
       <c r="T236" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U236" t="s">
         <v>392</v>
@@ -37871,7 +37871,7 @@
         <v>16</v>
       </c>
       <c r="T237" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U237" t="s">
         <v>392</v>
@@ -38615,7 +38615,7 @@
         <v>16</v>
       </c>
       <c r="T249" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U249" t="s">
         <v>392</v>
@@ -38677,7 +38677,7 @@
         <v>16</v>
       </c>
       <c r="T250" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U250" t="s">
         <v>392</v>
@@ -39793,7 +39793,7 @@
         <v>16</v>
       </c>
       <c r="T268" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U268" t="s">
         <v>392</v>
@@ -39855,7 +39855,7 @@
         <v>16</v>
       </c>
       <c r="T269" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U269" t="s">
         <v>392</v>
@@ -40723,7 +40723,7 @@
         <v>16</v>
       </c>
       <c r="T283" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U283" t="s">
         <v>392</v>
@@ -40785,7 +40785,7 @@
         <v>16</v>
       </c>
       <c r="T284" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U284" t="s">
         <v>392</v>
@@ -40847,7 +40847,7 @@
         <v>16</v>
       </c>
       <c r="T285" t="s">
-        <v>614</v>
+        <v>391</v>
       </c>
       <c r="U285" t="s">
         <v>392</v>
@@ -40909,7 +40909,7 @@
         <v>16</v>
       </c>
       <c r="T286" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="U286" t="s">
         <v>392</v>
@@ -41026,7 +41026,7 @@
         <v>33</v>
       </c>
       <c r="O289">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="290" spans="2:15" x14ac:dyDescent="0.45">
@@ -41055,7 +41055,7 @@
         <v>33</v>
       </c>
       <c r="O290">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="291" spans="2:15" x14ac:dyDescent="0.45">
@@ -41084,7 +41084,7 @@
         <v>33</v>
       </c>
       <c r="O291">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="292" spans="2:15" x14ac:dyDescent="0.45">
@@ -45235,7 +45235,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7E8BAB-84D9-4B6D-97E3-A907256700EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{426DF45D-D8FF-4160-BFE6-B7439A893898}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA93641B-D99C-4A9E-84CF-2873E1F5F09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EE17DCD-9F31-43EE-AB6A-713551C9B516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7DA27779-026B-45EA-8C26-C1CA6D278BDF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B39B0088-428E-4462-BA7A-8B94E3EB2153}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1904,13 +1904,13 @@
     <t>IRENA Gap - solar (2024) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 13_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2023) - 13_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2022) - 13_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 13_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2023) - 13_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>Aggregated Plant -- construction</t>
@@ -4141,7 +4141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D00F5127-A14D-41C3-A7F5-F54B9D9CB725}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8534C430-F10F-4AA9-A3A3-99F293C931B9}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15567,7 +15567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5019F4DD-BEBB-4C61-B1F1-DD16F1BCC5EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B0A1F3-052C-4278-9229-65889AAD1216}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23639,7 +23639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6C780D4-8ACB-4F22-873E-225FF1C65C96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E384D4FF-4ED7-44E0-81F0-ACE9FE7DA112}">
   <dimension ref="B9:Y413"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38213,7 +38213,7 @@
         <v>17</v>
       </c>
       <c r="U243" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V243" t="s">
         <v>395</v>
@@ -38275,7 +38275,7 @@
         <v>17</v>
       </c>
       <c r="U244" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V244" t="s">
         <v>395</v>
@@ -38337,7 +38337,7 @@
         <v>17</v>
       </c>
       <c r="U245" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V245" t="s">
         <v>395</v>
@@ -38399,7 +38399,7 @@
         <v>17</v>
       </c>
       <c r="U246" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V246" t="s">
         <v>395</v>
@@ -38895,7 +38895,7 @@
         <v>17</v>
       </c>
       <c r="U254" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V254" t="s">
         <v>395</v>
@@ -38957,7 +38957,7 @@
         <v>17</v>
       </c>
       <c r="U255" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V255" t="s">
         <v>395</v>
@@ -40259,7 +40259,7 @@
         <v>17</v>
       </c>
       <c r="U276" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V276" t="s">
         <v>395</v>
@@ -40321,7 +40321,7 @@
         <v>17</v>
       </c>
       <c r="U277" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V277" t="s">
         <v>395</v>
@@ -41189,7 +41189,7 @@
         <v>17</v>
       </c>
       <c r="U291" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V291" t="s">
         <v>395</v>
@@ -41251,7 +41251,7 @@
         <v>17</v>
       </c>
       <c r="U292" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V292" t="s">
         <v>395</v>
@@ -41313,7 +41313,7 @@
         <v>17</v>
       </c>
       <c r="U293" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V293" t="s">
         <v>395</v>
@@ -41375,7 +41375,7 @@
         <v>17</v>
       </c>
       <c r="U294" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V294" t="s">
         <v>395</v>
@@ -41454,7 +41454,7 @@
         <v>33</v>
       </c>
       <c r="P296">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="297" spans="2:25" x14ac:dyDescent="0.45">
@@ -41483,7 +41483,7 @@
         <v>32</v>
       </c>
       <c r="P297">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="298" spans="2:25" x14ac:dyDescent="0.45">
@@ -41512,7 +41512,7 @@
         <v>31</v>
       </c>
       <c r="P298">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="299" spans="2:25" x14ac:dyDescent="0.45">
@@ -41541,7 +41541,7 @@
         <v>33</v>
       </c>
       <c r="P299">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="300" spans="2:25" x14ac:dyDescent="0.45">
@@ -41570,7 +41570,7 @@
         <v>32</v>
       </c>
       <c r="P300">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="301" spans="2:25" x14ac:dyDescent="0.45">
@@ -41599,7 +41599,7 @@
         <v>31</v>
       </c>
       <c r="P301">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="302" spans="2:25" x14ac:dyDescent="0.45">
@@ -41628,7 +41628,7 @@
         <v>33</v>
       </c>
       <c r="P302">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="303" spans="2:25" x14ac:dyDescent="0.45">
@@ -41657,7 +41657,7 @@
         <v>32</v>
       </c>
       <c r="P303">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="304" spans="2:25" x14ac:dyDescent="0.45">
@@ -41686,7 +41686,7 @@
         <v>31</v>
       </c>
       <c r="P304">
-        <v>0.31219726448302754</v>
+        <v>0.31219726448302759</v>
       </c>
     </row>
     <row r="305" spans="2:16" x14ac:dyDescent="0.45">
@@ -45837,7 +45837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77EC86EA-404E-4719-BD0F-B61FCE418ABF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57E1758-1C04-4BF6-A99B-9E999B922180}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EE17DCD-9F31-43EE-AB6A-713551C9B516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4FA854C-7A6F-4EA8-8925-CB22DB119722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B39B0088-428E-4462-BA7A-8B94E3EB2153}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8C613F82-757C-4E6A-8C31-826DD0C003B6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1883,34 +1883,34 @@
     <t>Włocławek hydroelectric plant_ -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 10_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2022) - 10_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2023) - 10_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2024) - 10_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 11_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2022) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 11_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2024) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2022) - 13_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 13_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2023) - 13_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 13_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>Aggregated Plant -- construction</t>
@@ -4141,7 +4141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8534C430-F10F-4AA9-A3A3-99F293C931B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BAFAE27-DE87-4ED0-9E03-702C77FEC776}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15567,7 +15567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B0A1F3-052C-4278-9229-65889AAD1216}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F260BA-D182-4413-ADBE-F8D1CD1C81ED}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23639,7 +23639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E384D4FF-4ED7-44E0-81F0-ACE9FE7DA112}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D4A397-03A8-4DAD-BB87-21C449ED39E1}">
   <dimension ref="B9:Y413"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38213,7 +38213,7 @@
         <v>17</v>
       </c>
       <c r="U243" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V243" t="s">
         <v>395</v>
@@ -38275,7 +38275,7 @@
         <v>17</v>
       </c>
       <c r="U244" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V244" t="s">
         <v>395</v>
@@ -38337,7 +38337,7 @@
         <v>17</v>
       </c>
       <c r="U245" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V245" t="s">
         <v>395</v>
@@ -38399,7 +38399,7 @@
         <v>17</v>
       </c>
       <c r="U246" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V246" t="s">
         <v>395</v>
@@ -38895,7 +38895,7 @@
         <v>17</v>
       </c>
       <c r="U254" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V254" t="s">
         <v>395</v>
@@ -38957,7 +38957,7 @@
         <v>17</v>
       </c>
       <c r="U255" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V255" t="s">
         <v>395</v>
@@ -39019,7 +39019,7 @@
         <v>17</v>
       </c>
       <c r="U256" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V256" t="s">
         <v>395</v>
@@ -39081,7 +39081,7 @@
         <v>17</v>
       </c>
       <c r="U257" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V257" t="s">
         <v>395</v>
@@ -40259,7 +40259,7 @@
         <v>17</v>
       </c>
       <c r="U276" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V276" t="s">
         <v>395</v>
@@ -40321,7 +40321,7 @@
         <v>17</v>
       </c>
       <c r="U277" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V277" t="s">
         <v>395</v>
@@ -41189,7 +41189,7 @@
         <v>17</v>
       </c>
       <c r="U291" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V291" t="s">
         <v>395</v>
@@ -41251,7 +41251,7 @@
         <v>17</v>
       </c>
       <c r="U292" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V292" t="s">
         <v>395</v>
@@ -41313,7 +41313,7 @@
         <v>17</v>
       </c>
       <c r="U293" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V293" t="s">
         <v>395</v>
@@ -41375,7 +41375,7 @@
         <v>17</v>
       </c>
       <c r="U294" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V294" t="s">
         <v>395</v>
@@ -41454,7 +41454,7 @@
         <v>33</v>
       </c>
       <c r="P296">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="297" spans="2:25" x14ac:dyDescent="0.45">
@@ -41483,7 +41483,7 @@
         <v>32</v>
       </c>
       <c r="P297">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="298" spans="2:25" x14ac:dyDescent="0.45">
@@ -41512,7 +41512,7 @@
         <v>31</v>
       </c>
       <c r="P298">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="299" spans="2:25" x14ac:dyDescent="0.45">
@@ -41541,7 +41541,7 @@
         <v>33</v>
       </c>
       <c r="P299">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="300" spans="2:25" x14ac:dyDescent="0.45">
@@ -41570,7 +41570,7 @@
         <v>32</v>
       </c>
       <c r="P300">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="301" spans="2:25" x14ac:dyDescent="0.45">
@@ -41599,7 +41599,7 @@
         <v>31</v>
       </c>
       <c r="P301">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="302" spans="2:25" x14ac:dyDescent="0.45">
@@ -41628,7 +41628,7 @@
         <v>33</v>
       </c>
       <c r="P302">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="303" spans="2:25" x14ac:dyDescent="0.45">
@@ -41657,7 +41657,7 @@
         <v>32</v>
       </c>
       <c r="P303">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="304" spans="2:25" x14ac:dyDescent="0.45">
@@ -41686,7 +41686,7 @@
         <v>31</v>
       </c>
       <c r="P304">
-        <v>0.31219726448302759</v>
+        <v>0.31219726448302748</v>
       </c>
     </row>
     <row r="305" spans="2:16" x14ac:dyDescent="0.45">
@@ -45837,7 +45837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57E1758-1C04-4BF6-A99B-9E999B922180}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDB9681-2A21-4F14-B2C5-093E4C5040F6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4FA854C-7A6F-4EA8-8925-CB22DB119722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{882D34BE-00E5-4233-8CAE-3B2CDE0735B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8C613F82-757C-4E6A-8C31-826DD0C003B6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A5166145-7D81-48C7-A27B-76C1CDDB098A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1883,34 +1883,34 @@
     <t>Włocławek hydroelectric plant_ -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2022) - 10_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2023) - 10_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 10_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2024) - 10_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2023) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 11_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2022) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2024) - 11_Missing Solar Capacity -- operating</t>
+    <t>IRENA Gap - solar (2024) - 13_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2023) - 13_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2022) - 13_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 13_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2023) - 13_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>Aggregated Plant -- construction</t>
@@ -4141,7 +4141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BAFAE27-DE87-4ED0-9E03-702C77FEC776}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8200C2D1-6637-4929-8D01-7F8691B90C01}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15567,7 +15567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F260BA-D182-4413-ADBE-F8D1CD1C81ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACEF850-0E61-42AB-9D2E-07BD244219DB}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23639,7 +23639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D4A397-03A8-4DAD-BB87-21C449ED39E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACAFA96-EEE0-49CF-BE4C-661B98E7FFDE}">
   <dimension ref="B9:Y413"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37653,7 +37653,7 @@
         <v>33</v>
       </c>
       <c r="P233">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="R233" t="s">
         <v>393</v>
@@ -37706,7 +37706,7 @@
         <v>32</v>
       </c>
       <c r="P234">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="R234" t="s">
         <v>393</v>
@@ -37759,7 +37759,7 @@
         <v>31</v>
       </c>
       <c r="P235">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="R235" t="s">
         <v>393</v>
@@ -37812,7 +37812,7 @@
         <v>33</v>
       </c>
       <c r="P236">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="R236" t="s">
         <v>393</v>
@@ -37865,7 +37865,7 @@
         <v>32</v>
       </c>
       <c r="P237">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="R237" t="s">
         <v>393</v>
@@ -37918,7 +37918,7 @@
         <v>31</v>
       </c>
       <c r="P238">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="R238" t="s">
         <v>393</v>
@@ -37971,7 +37971,7 @@
         <v>33</v>
       </c>
       <c r="P239">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="R239" t="s">
         <v>393</v>
@@ -38024,7 +38024,7 @@
         <v>32</v>
       </c>
       <c r="P240">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="R240" t="s">
         <v>393</v>
@@ -38077,7 +38077,7 @@
         <v>31</v>
       </c>
       <c r="P241">
-        <v>0.13941713559017349</v>
+        <v>0.13941713559017346</v>
       </c>
       <c r="R241" t="s">
         <v>393</v>
@@ -38213,7 +38213,7 @@
         <v>17</v>
       </c>
       <c r="U243" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V243" t="s">
         <v>395</v>
@@ -38275,7 +38275,7 @@
         <v>17</v>
       </c>
       <c r="U244" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V244" t="s">
         <v>395</v>
@@ -38337,7 +38337,7 @@
         <v>17</v>
       </c>
       <c r="U245" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V245" t="s">
         <v>395</v>
@@ -38399,7 +38399,7 @@
         <v>17</v>
       </c>
       <c r="U246" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V246" t="s">
         <v>395</v>
@@ -38895,7 +38895,7 @@
         <v>17</v>
       </c>
       <c r="U254" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V254" t="s">
         <v>395</v>
@@ -38957,7 +38957,7 @@
         <v>17</v>
       </c>
       <c r="U255" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V255" t="s">
         <v>395</v>
@@ -40259,7 +40259,7 @@
         <v>17</v>
       </c>
       <c r="U276" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V276" t="s">
         <v>395</v>
@@ -40321,7 +40321,7 @@
         <v>17</v>
       </c>
       <c r="U277" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V277" t="s">
         <v>395</v>
@@ -40445,7 +40445,7 @@
         <v>17</v>
       </c>
       <c r="U279" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V279" t="s">
         <v>395</v>
@@ -40507,7 +40507,7 @@
         <v>17</v>
       </c>
       <c r="U280" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V280" t="s">
         <v>395</v>
@@ -41189,7 +41189,7 @@
         <v>17</v>
       </c>
       <c r="U291" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V291" t="s">
         <v>395</v>
@@ -41251,7 +41251,7 @@
         <v>17</v>
       </c>
       <c r="U292" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V292" t="s">
         <v>395</v>
@@ -41454,7 +41454,7 @@
         <v>33</v>
       </c>
       <c r="P296">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="297" spans="2:25" x14ac:dyDescent="0.45">
@@ -41483,7 +41483,7 @@
         <v>32</v>
       </c>
       <c r="P297">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="298" spans="2:25" x14ac:dyDescent="0.45">
@@ -41512,7 +41512,7 @@
         <v>31</v>
       </c>
       <c r="P298">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="299" spans="2:25" x14ac:dyDescent="0.45">
@@ -41541,7 +41541,7 @@
         <v>33</v>
       </c>
       <c r="P299">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="300" spans="2:25" x14ac:dyDescent="0.45">
@@ -41570,7 +41570,7 @@
         <v>32</v>
       </c>
       <c r="P300">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="301" spans="2:25" x14ac:dyDescent="0.45">
@@ -41599,7 +41599,7 @@
         <v>31</v>
       </c>
       <c r="P301">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="302" spans="2:25" x14ac:dyDescent="0.45">
@@ -41628,7 +41628,7 @@
         <v>33</v>
       </c>
       <c r="P302">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="303" spans="2:25" x14ac:dyDescent="0.45">
@@ -41657,7 +41657,7 @@
         <v>32</v>
       </c>
       <c r="P303">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="304" spans="2:25" x14ac:dyDescent="0.45">
@@ -41686,7 +41686,7 @@
         <v>31</v>
       </c>
       <c r="P304">
-        <v>0.31219726448302748</v>
+        <v>0.31219726448302754</v>
       </c>
     </row>
     <row r="305" spans="2:16" x14ac:dyDescent="0.45">
@@ -45837,7 +45837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDB9681-2A21-4F14-B2C5-093E4C5040F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D78EF8BC-C7BA-40A6-8990-F2372EFA7DD5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{882D34BE-00E5-4233-8CAE-3B2CDE0735B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64AB7E41-8B64-4816-8BDE-11DB15B37848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A5166145-7D81-48C7-A27B-76C1CDDB098A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FCE96AF7-2810-4D85-AF40-0C2C04B544B2}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1883,34 +1883,34 @@
     <t>Włocławek hydroelectric plant_ -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 10_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2024) - 10_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2022) - 10_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2023) - 10_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 10_Missing Solar Capacity -- operating</t>
+    <t>IRENA Gap - solar (2024) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2023) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2024) - 11_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2022) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 13_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2022) - 13_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 13_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2023) - 13_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 13_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>Aggregated Plant -- construction</t>
@@ -4141,7 +4141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8200C2D1-6637-4929-8D01-7F8691B90C01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC24A17-0A2D-435C-8DFE-981EC7DCE339}">
   <dimension ref="B9:V193"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15567,7 +15567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACEF850-0E61-42AB-9D2E-07BD244219DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D77D238-04F8-4E8F-BB4A-AF04105CAE23}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23639,7 +23639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACAFA96-EEE0-49CF-BE4C-661B98E7FFDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972492F2-ECFD-4D68-BD3B-C7E23CF9402E}">
   <dimension ref="B9:Y413"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37653,7 +37653,7 @@
         <v>33</v>
       </c>
       <c r="P233">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="R233" t="s">
         <v>393</v>
@@ -37706,7 +37706,7 @@
         <v>32</v>
       </c>
       <c r="P234">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="R234" t="s">
         <v>393</v>
@@ -37759,7 +37759,7 @@
         <v>31</v>
       </c>
       <c r="P235">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="R235" t="s">
         <v>393</v>
@@ -37812,7 +37812,7 @@
         <v>33</v>
       </c>
       <c r="P236">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="R236" t="s">
         <v>393</v>
@@ -37865,7 +37865,7 @@
         <v>32</v>
       </c>
       <c r="P237">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="R237" t="s">
         <v>393</v>
@@ -37918,7 +37918,7 @@
         <v>31</v>
       </c>
       <c r="P238">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="R238" t="s">
         <v>393</v>
@@ -37971,7 +37971,7 @@
         <v>33</v>
       </c>
       <c r="P239">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="R239" t="s">
         <v>393</v>
@@ -38024,7 +38024,7 @@
         <v>32</v>
       </c>
       <c r="P240">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="R240" t="s">
         <v>393</v>
@@ -38077,7 +38077,7 @@
         <v>31</v>
       </c>
       <c r="P241">
-        <v>0.13941713559017346</v>
+        <v>0.13941713559017349</v>
       </c>
       <c r="R241" t="s">
         <v>393</v>
@@ -38213,7 +38213,7 @@
         <v>17</v>
       </c>
       <c r="U243" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V243" t="s">
         <v>395</v>
@@ -38275,7 +38275,7 @@
         <v>17</v>
       </c>
       <c r="U244" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V244" t="s">
         <v>395</v>
@@ -38337,7 +38337,7 @@
         <v>17</v>
       </c>
       <c r="U245" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V245" t="s">
         <v>395</v>
@@ -38399,7 +38399,7 @@
         <v>17</v>
       </c>
       <c r="U246" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V246" t="s">
         <v>395</v>
@@ -38895,7 +38895,7 @@
         <v>17</v>
       </c>
       <c r="U254" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V254" t="s">
         <v>395</v>
@@ -38957,7 +38957,7 @@
         <v>17</v>
       </c>
       <c r="U255" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V255" t="s">
         <v>395</v>
@@ -39825,7 +39825,7 @@
         <v>17</v>
       </c>
       <c r="U269" t="s">
-        <v>394</v>
+        <v>627</v>
       </c>
       <c r="V269" t="s">
         <v>395</v>
@@ -39837,7 +39837,7 @@
         <v>614</v>
       </c>
       <c r="Y269" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="270" spans="2:25" x14ac:dyDescent="0.45">
@@ -39887,7 +39887,7 @@
         <v>17</v>
       </c>
       <c r="U270" t="s">
-        <v>627</v>
+        <v>394</v>
       </c>
       <c r="V270" t="s">
         <v>395</v>
@@ -39899,7 +39899,7 @@
         <v>614</v>
       </c>
       <c r="Y270" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="271" spans="2:25" x14ac:dyDescent="0.45">
@@ -40259,7 +40259,7 @@
         <v>17</v>
       </c>
       <c r="U276" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V276" t="s">
         <v>395</v>
@@ -40321,7 +40321,7 @@
         <v>17</v>
       </c>
       <c r="U277" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V277" t="s">
         <v>395</v>
@@ -41189,7 +41189,7 @@
         <v>17</v>
       </c>
       <c r="U291" t="s">
-        <v>394</v>
+        <v>623</v>
       </c>
       <c r="V291" t="s">
         <v>395</v>
@@ -41251,7 +41251,7 @@
         <v>17</v>
       </c>
       <c r="U292" t="s">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="V292" t="s">
         <v>395</v>
@@ -45837,7 +45837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D78EF8BC-C7BA-40A6-8990-F2372EFA7DD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6097883D-7154-4201-BA6C-C795FA05052D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan50/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEED03FC-4E3E-490B-A8B8-85D3A439A15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31DC9A8B-92B2-4953-8F81-D86E5E31C3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" xr2:uid="{2A949578-7B92-4FEF-8055-337EE99C2AC8}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" xr2:uid="{1C3394C8-4FA7-40FF-AC36-FF4980D7F76F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2381,19 +2381,19 @@
     <t>IRENA Gap - solar (2023) - 17_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2022) - 35_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2023) - 35_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 35_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 35_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 35_Missing Solar Capacity -- operating</t>
+    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
@@ -3677,7 +3677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9894346-709B-4C70-A1F6-CCACC86F1C0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF92A78-DC95-4372-9595-F7573720250F}">
   <dimension ref="B9:Y47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6186,7 +6186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E22D1F3C-658F-439F-A846-6A48D6768A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0DFBA2B-C93F-4582-80AC-64E028251208}">
   <dimension ref="B9:Y160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14306,7 +14306,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D13ADBB-1F1D-46E7-85F0-3114CC2C6D73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABF4603-7125-410B-8223-E95F7D60850C}">
   <dimension ref="B9:Y723"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28320,7 +28320,7 @@
         <v>33</v>
       </c>
       <c r="P233">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R233" t="s">
         <v>558</v>
@@ -28373,7 +28373,7 @@
         <v>32</v>
       </c>
       <c r="P234">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R234" t="s">
         <v>558</v>
@@ -28426,7 +28426,7 @@
         <v>31</v>
       </c>
       <c r="P235">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R235" t="s">
         <v>558</v>
@@ -28479,7 +28479,7 @@
         <v>33</v>
       </c>
       <c r="P236">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R236" t="s">
         <v>558</v>
@@ -28532,7 +28532,7 @@
         <v>32</v>
       </c>
       <c r="P237">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R237" t="s">
         <v>558</v>
@@ -28585,7 +28585,7 @@
         <v>31</v>
       </c>
       <c r="P238">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R238" t="s">
         <v>558</v>
@@ -28638,7 +28638,7 @@
         <v>33</v>
       </c>
       <c r="P239">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R239" t="s">
         <v>558</v>
@@ -28691,7 +28691,7 @@
         <v>32</v>
       </c>
       <c r="P240">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R240" t="s">
         <v>558</v>
@@ -28744,7 +28744,7 @@
         <v>31</v>
       </c>
       <c r="P241">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R241" t="s">
         <v>558</v>
@@ -28797,7 +28797,7 @@
         <v>33</v>
       </c>
       <c r="P242">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R242" t="s">
         <v>558</v>
@@ -28850,7 +28850,7 @@
         <v>32</v>
       </c>
       <c r="P243">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R243" t="s">
         <v>558</v>
@@ -28903,7 +28903,7 @@
         <v>31</v>
       </c>
       <c r="P244">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R244" t="s">
         <v>558</v>
@@ -28956,7 +28956,7 @@
         <v>33</v>
       </c>
       <c r="P245">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R245" t="s">
         <v>558</v>
@@ -29009,7 +29009,7 @@
         <v>32</v>
       </c>
       <c r="P246">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R246" t="s">
         <v>558</v>
@@ -29062,7 +29062,7 @@
         <v>31</v>
       </c>
       <c r="P247">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R247" t="s">
         <v>558</v>
@@ -29115,7 +29115,7 @@
         <v>33</v>
       </c>
       <c r="P248">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R248" t="s">
         <v>558</v>
@@ -29127,7 +29127,7 @@
         <v>17</v>
       </c>
       <c r="U248" t="s">
-        <v>779</v>
+        <v>559</v>
       </c>
       <c r="V248" t="s">
         <v>560</v>
@@ -29139,7 +29139,7 @@
         <v>778</v>
       </c>
       <c r="Y248" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="249" spans="2:25" x14ac:dyDescent="0.45">
@@ -29168,7 +29168,7 @@
         <v>32</v>
       </c>
       <c r="P249">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R249" t="s">
         <v>558</v>
@@ -29180,7 +29180,7 @@
         <v>17</v>
       </c>
       <c r="U249" t="s">
-        <v>559</v>
+        <v>779</v>
       </c>
       <c r="V249" t="s">
         <v>560</v>
@@ -29192,7 +29192,7 @@
         <v>778</v>
       </c>
       <c r="Y249" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="250" spans="2:25" x14ac:dyDescent="0.45">
@@ -29221,7 +29221,7 @@
         <v>31</v>
       </c>
       <c r="P250">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R250" t="s">
         <v>558</v>
@@ -29274,7 +29274,7 @@
         <v>33</v>
       </c>
       <c r="P251">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R251" t="s">
         <v>558</v>
@@ -29327,7 +29327,7 @@
         <v>32</v>
       </c>
       <c r="P252">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R252" t="s">
         <v>558</v>
@@ -29380,7 +29380,7 @@
         <v>31</v>
       </c>
       <c r="P253">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R253" t="s">
         <v>558</v>
@@ -29433,7 +29433,7 @@
         <v>33</v>
       </c>
       <c r="P254">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R254" t="s">
         <v>558</v>
@@ -29486,7 +29486,7 @@
         <v>32</v>
       </c>
       <c r="P255">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R255" t="s">
         <v>558</v>
@@ -29539,7 +29539,7 @@
         <v>31</v>
       </c>
       <c r="P256">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R256" t="s">
         <v>558</v>
@@ -29592,7 +29592,7 @@
         <v>33</v>
       </c>
       <c r="P257">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R257" t="s">
         <v>558</v>
@@ -29645,7 +29645,7 @@
         <v>32</v>
       </c>
       <c r="P258">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R258" t="s">
         <v>558</v>
@@ -29698,7 +29698,7 @@
         <v>31</v>
       </c>
       <c r="P259">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R259" t="s">
         <v>558</v>
@@ -29751,7 +29751,7 @@
         <v>33</v>
       </c>
       <c r="P260">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R260" t="s">
         <v>558</v>
@@ -29804,7 +29804,7 @@
         <v>32</v>
       </c>
       <c r="P261">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R261" t="s">
         <v>558</v>
@@ -29857,7 +29857,7 @@
         <v>31</v>
       </c>
       <c r="P262">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R262" t="s">
         <v>558</v>
@@ -29910,7 +29910,7 @@
         <v>33</v>
       </c>
       <c r="P263">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R263" t="s">
         <v>558</v>
@@ -29963,7 +29963,7 @@
         <v>32</v>
       </c>
       <c r="P264">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R264" t="s">
         <v>558</v>
@@ -30016,7 +30016,7 @@
         <v>31</v>
       </c>
       <c r="P265">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R265" t="s">
         <v>558</v>
@@ -30069,7 +30069,7 @@
         <v>33</v>
       </c>
       <c r="P266">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R266" t="s">
         <v>558</v>
@@ -30122,7 +30122,7 @@
         <v>32</v>
       </c>
       <c r="P267">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R267" t="s">
         <v>558</v>
@@ -30175,7 +30175,7 @@
         <v>31</v>
       </c>
       <c r="P268">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R268" t="s">
         <v>558</v>
@@ -30228,7 +30228,7 @@
         <v>33</v>
       </c>
       <c r="P269">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R269" t="s">
         <v>558</v>
@@ -30281,7 +30281,7 @@
         <v>32</v>
       </c>
       <c r="P270">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R270" t="s">
         <v>558</v>
@@ -30334,7 +30334,7 @@
         <v>31</v>
       </c>
       <c r="P271">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R271" t="s">
         <v>558</v>
@@ -30387,7 +30387,7 @@
         <v>33</v>
       </c>
       <c r="P272">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R272" t="s">
         <v>558</v>
@@ -30440,7 +30440,7 @@
         <v>32</v>
       </c>
       <c r="P273">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R273" t="s">
         <v>558</v>
@@ -30493,7 +30493,7 @@
         <v>31</v>
       </c>
       <c r="P274">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R274" t="s">
         <v>558</v>
@@ -30546,7 +30546,7 @@
         <v>33</v>
       </c>
       <c r="P275">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R275" t="s">
         <v>558</v>
@@ -30599,7 +30599,7 @@
         <v>32</v>
       </c>
       <c r="P276">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R276" t="s">
         <v>558</v>
@@ -30652,7 +30652,7 @@
         <v>31</v>
       </c>
       <c r="P277">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R277" t="s">
         <v>558</v>
@@ -30705,7 +30705,7 @@
         <v>33</v>
       </c>
       <c r="P278">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R278" t="s">
         <v>558</v>
@@ -30758,7 +30758,7 @@
         <v>32</v>
       </c>
       <c r="P279">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R279" t="s">
         <v>558</v>
@@ -30811,7 +30811,7 @@
         <v>31</v>
       </c>
       <c r="P280">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R280" t="s">
         <v>558</v>
@@ -30864,7 +30864,7 @@
         <v>33</v>
       </c>
       <c r="P281">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R281" t="s">
         <v>558</v>
@@ -30917,7 +30917,7 @@
         <v>32</v>
       </c>
       <c r="P282">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R282" t="s">
         <v>558</v>
@@ -30970,7 +30970,7 @@
         <v>31</v>
       </c>
       <c r="P283">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R283" t="s">
         <v>558</v>
@@ -31023,7 +31023,7 @@
         <v>33</v>
       </c>
       <c r="P284">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R284" t="s">
         <v>558</v>
@@ -31076,7 +31076,7 @@
         <v>32</v>
       </c>
       <c r="P285">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R285" t="s">
         <v>558</v>
@@ -31129,7 +31129,7 @@
         <v>31</v>
       </c>
       <c r="P286">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R286" t="s">
         <v>558</v>
@@ -31182,7 +31182,7 @@
         <v>33</v>
       </c>
       <c r="P287">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R287" t="s">
         <v>558</v>
@@ -31235,7 +31235,7 @@
         <v>32</v>
       </c>
       <c r="P288">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R288" t="s">
         <v>558</v>
@@ -31288,7 +31288,7 @@
         <v>31</v>
       </c>
       <c r="P289">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R289" t="s">
         <v>558</v>
@@ -31341,7 +31341,7 @@
         <v>33</v>
       </c>
       <c r="P290">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R290" t="s">
         <v>558</v>
@@ -31394,7 +31394,7 @@
         <v>32</v>
       </c>
       <c r="P291">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R291" t="s">
         <v>558</v>
@@ -31447,7 +31447,7 @@
         <v>31</v>
       </c>
       <c r="P292">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R292" t="s">
         <v>558</v>
@@ -31500,7 +31500,7 @@
         <v>33</v>
       </c>
       <c r="P293">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R293" t="s">
         <v>558</v>
@@ -31512,7 +31512,7 @@
         <v>17</v>
       </c>
       <c r="U293" t="s">
-        <v>790</v>
+        <v>559</v>
       </c>
       <c r="V293" t="s">
         <v>560</v>
@@ -31553,7 +31553,7 @@
         <v>32</v>
       </c>
       <c r="P294">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R294" t="s">
         <v>558</v>
@@ -31565,7 +31565,7 @@
         <v>17</v>
       </c>
       <c r="U294" t="s">
-        <v>559</v>
+        <v>790</v>
       </c>
       <c r="V294" t="s">
         <v>560</v>
@@ -31606,7 +31606,7 @@
         <v>31</v>
       </c>
       <c r="P295">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R295" t="s">
         <v>558</v>
@@ -31659,7 +31659,7 @@
         <v>33</v>
       </c>
       <c r="P296">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R296" t="s">
         <v>558</v>
@@ -31712,7 +31712,7 @@
         <v>32</v>
       </c>
       <c r="P297">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R297" t="s">
         <v>558</v>
@@ -31765,7 +31765,7 @@
         <v>31</v>
       </c>
       <c r="P298">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R298" t="s">
         <v>558</v>
@@ -31818,7 +31818,7 @@
         <v>33</v>
       </c>
       <c r="P299">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R299" t="s">
         <v>558</v>
@@ -31871,7 +31871,7 @@
         <v>32</v>
       </c>
       <c r="P300">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R300" t="s">
         <v>558</v>
@@ -31924,7 +31924,7 @@
         <v>31</v>
       </c>
       <c r="P301">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R301" t="s">
         <v>558</v>
@@ -31977,7 +31977,7 @@
         <v>33</v>
       </c>
       <c r="P302">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R302" t="s">
         <v>558</v>
@@ -32030,7 +32030,7 @@
         <v>32</v>
       </c>
       <c r="P303">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R303" t="s">
         <v>558</v>
@@ -32083,7 +32083,7 @@
         <v>31</v>
       </c>
       <c r="P304">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R304" t="s">
         <v>558</v>
@@ -32136,7 +32136,7 @@
         <v>33</v>
       </c>
       <c r="P305">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R305" t="s">
         <v>558</v>
@@ -32189,7 +32189,7 @@
         <v>32</v>
       </c>
       <c r="P306">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R306" t="s">
         <v>558</v>
@@ -32242,7 +32242,7 @@
         <v>31</v>
       </c>
       <c r="P307">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R307" t="s">
         <v>558</v>
@@ -32295,7 +32295,7 @@
         <v>33</v>
       </c>
       <c r="P308">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R308" t="s">
         <v>558</v>
@@ -32307,7 +32307,7 @@
         <v>17</v>
       </c>
       <c r="U308" t="s">
-        <v>790</v>
+        <v>559</v>
       </c>
       <c r="V308" t="s">
         <v>560</v>
@@ -32348,7 +32348,7 @@
         <v>32</v>
       </c>
       <c r="P309">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R309" t="s">
         <v>558</v>
@@ -32360,7 +32360,7 @@
         <v>17</v>
       </c>
       <c r="U309" t="s">
-        <v>559</v>
+        <v>790</v>
       </c>
       <c r="V309" t="s">
         <v>560</v>
@@ -32401,7 +32401,7 @@
         <v>31</v>
       </c>
       <c r="P310">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R310" t="s">
         <v>558</v>
@@ -32454,7 +32454,7 @@
         <v>33</v>
       </c>
       <c r="P311">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R311" t="s">
         <v>558</v>
@@ -32507,7 +32507,7 @@
         <v>32</v>
       </c>
       <c r="P312">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R312" t="s">
         <v>558</v>
@@ -32560,7 +32560,7 @@
         <v>31</v>
       </c>
       <c r="P313">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R313" t="s">
         <v>558</v>
@@ -32613,7 +32613,7 @@
         <v>33</v>
       </c>
       <c r="P314">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R314" t="s">
         <v>558</v>
@@ -32666,7 +32666,7 @@
         <v>32</v>
       </c>
       <c r="P315">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R315" t="s">
         <v>558</v>
@@ -32719,7 +32719,7 @@
         <v>31</v>
       </c>
       <c r="P316">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R316" t="s">
         <v>558</v>
@@ -32772,7 +32772,7 @@
         <v>33</v>
       </c>
       <c r="P317">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R317" t="s">
         <v>558</v>
@@ -32825,7 +32825,7 @@
         <v>32</v>
       </c>
       <c r="P318">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R318" t="s">
         <v>558</v>
@@ -32878,7 +32878,7 @@
         <v>31</v>
       </c>
       <c r="P319">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R319" t="s">
         <v>558</v>
@@ -32931,7 +32931,7 @@
         <v>33</v>
       </c>
       <c r="P320">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R320" t="s">
         <v>558</v>
@@ -32984,7 +32984,7 @@
         <v>32</v>
       </c>
       <c r="P321">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R321" t="s">
         <v>558</v>
@@ -33037,7 +33037,7 @@
         <v>31</v>
       </c>
       <c r="P322">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R322" t="s">
         <v>558</v>
@@ -33090,7 +33090,7 @@
         <v>33</v>
       </c>
       <c r="P323">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R323" t="s">
         <v>558</v>
@@ -33143,7 +33143,7 @@
         <v>32</v>
       </c>
       <c r="P324">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R324" t="s">
         <v>558</v>
@@ -33155,7 +33155,7 @@
         <v>17</v>
       </c>
       <c r="U324" t="s">
-        <v>790</v>
+        <v>559</v>
       </c>
       <c r="V324" t="s">
         <v>560</v>
@@ -33196,7 +33196,7 @@
         <v>31</v>
       </c>
       <c r="P325">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R325" t="s">
         <v>558</v>
@@ -33208,7 +33208,7 @@
         <v>17</v>
       </c>
       <c r="U325" t="s">
-        <v>559</v>
+        <v>790</v>
       </c>
       <c r="V325" t="s">
         <v>560</v>
@@ -33249,7 +33249,7 @@
         <v>33</v>
       </c>
       <c r="P326">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R326" t="s">
         <v>558</v>
@@ -33302,7 +33302,7 @@
         <v>32</v>
       </c>
       <c r="P327">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R327" t="s">
         <v>558</v>
@@ -33355,7 +33355,7 @@
         <v>31</v>
       </c>
       <c r="P328">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R328" t="s">
         <v>558</v>
@@ -33408,7 +33408,7 @@
         <v>33</v>
       </c>
       <c r="P329">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R329" t="s">
         <v>558</v>
@@ -33461,7 +33461,7 @@
         <v>32</v>
       </c>
       <c r="P330">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R330" t="s">
         <v>558</v>
@@ -33514,7 +33514,7 @@
         <v>31</v>
       </c>
       <c r="P331">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R331" t="s">
         <v>558</v>
@@ -33567,7 +33567,7 @@
         <v>33</v>
       </c>
       <c r="P332">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R332" t="s">
         <v>558</v>
@@ -33620,7 +33620,7 @@
         <v>32</v>
       </c>
       <c r="P333">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R333" t="s">
         <v>558</v>
@@ -33673,7 +33673,7 @@
         <v>31</v>
       </c>
       <c r="P334">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R334" t="s">
         <v>558</v>
@@ -33726,7 +33726,7 @@
         <v>33</v>
       </c>
       <c r="P335">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R335" t="s">
         <v>558</v>
@@ -33779,7 +33779,7 @@
         <v>32</v>
       </c>
       <c r="P336">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R336" t="s">
         <v>558</v>
@@ -33832,7 +33832,7 @@
         <v>31</v>
       </c>
       <c r="P337">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R337" t="s">
         <v>558</v>
@@ -33885,7 +33885,7 @@
         <v>33</v>
       </c>
       <c r="P338">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R338" t="s">
         <v>558</v>
@@ -33938,7 +33938,7 @@
         <v>32</v>
       </c>
       <c r="P339">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R339" t="s">
         <v>558</v>
@@ -33991,7 +33991,7 @@
         <v>31</v>
       </c>
       <c r="P340">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R340" t="s">
         <v>558</v>
@@ -34044,7 +34044,7 @@
         <v>33</v>
       </c>
       <c r="P341">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R341" t="s">
         <v>558</v>
@@ -34097,7 +34097,7 @@
         <v>32</v>
       </c>
       <c r="P342">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R342" t="s">
         <v>558</v>
@@ -34150,7 +34150,7 @@
         <v>31</v>
       </c>
       <c r="P343">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R343" t="s">
         <v>558</v>
@@ -34203,7 +34203,7 @@
         <v>33</v>
       </c>
       <c r="P344">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R344" t="s">
         <v>558</v>
@@ -34256,7 +34256,7 @@
         <v>32</v>
       </c>
       <c r="P345">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R345" t="s">
         <v>558</v>
@@ -34309,7 +34309,7 @@
         <v>31</v>
       </c>
       <c r="P346">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R346" t="s">
         <v>558</v>
@@ -34362,7 +34362,7 @@
         <v>33</v>
       </c>
       <c r="P347">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R347" t="s">
         <v>558</v>
@@ -34415,7 +34415,7 @@
         <v>32</v>
       </c>
       <c r="P348">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R348" t="s">
         <v>558</v>
@@ -34468,7 +34468,7 @@
         <v>31</v>
       </c>
       <c r="P349">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R349" t="s">
         <v>558</v>
@@ -34521,7 +34521,7 @@
         <v>33</v>
       </c>
       <c r="P350">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R350" t="s">
         <v>558</v>
@@ -34574,7 +34574,7 @@
         <v>32</v>
       </c>
       <c r="P351">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R351" t="s">
         <v>558</v>
@@ -34627,7 +34627,7 @@
         <v>31</v>
       </c>
       <c r="P352">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R352" t="s">
         <v>558</v>
@@ -34680,7 +34680,7 @@
         <v>33</v>
       </c>
       <c r="P353">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R353" t="s">
         <v>558</v>
@@ -34733,7 +34733,7 @@
         <v>32</v>
       </c>
       <c r="P354">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R354" t="s">
         <v>558</v>
@@ -34786,7 +34786,7 @@
         <v>31</v>
       </c>
       <c r="P355">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R355" t="s">
         <v>558</v>
@@ -34839,7 +34839,7 @@
         <v>33</v>
       </c>
       <c r="P356">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R356" t="s">
         <v>558</v>
@@ -34892,7 +34892,7 @@
         <v>32</v>
       </c>
       <c r="P357">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R357" t="s">
         <v>558</v>
@@ -34945,7 +34945,7 @@
         <v>31</v>
       </c>
       <c r="P358">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R358" t="s">
         <v>558</v>
@@ -34998,7 +34998,7 @@
         <v>33</v>
       </c>
       <c r="P359">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R359" t="s">
         <v>558</v>
@@ -35051,7 +35051,7 @@
         <v>32</v>
       </c>
       <c r="P360">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R360" t="s">
         <v>558</v>
@@ -35104,7 +35104,7 @@
         <v>31</v>
       </c>
       <c r="P361">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R361" t="s">
         <v>558</v>
@@ -35157,7 +35157,7 @@
         <v>33</v>
       </c>
       <c r="P362">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R362" t="s">
         <v>558</v>
@@ -35210,7 +35210,7 @@
         <v>32</v>
       </c>
       <c r="P363">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R363" t="s">
         <v>558</v>
@@ -35263,7 +35263,7 @@
         <v>31</v>
       </c>
       <c r="P364">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R364" t="s">
         <v>558</v>
@@ -35316,7 +35316,7 @@
         <v>33</v>
       </c>
       <c r="P365">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R365" t="s">
         <v>558</v>
@@ -35369,7 +35369,7 @@
         <v>32</v>
       </c>
       <c r="P366">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R366" t="s">
         <v>558</v>
@@ -35422,7 +35422,7 @@
         <v>31</v>
       </c>
       <c r="P367">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R367" t="s">
         <v>558</v>
@@ -35475,7 +35475,7 @@
         <v>33</v>
       </c>
       <c r="P368">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R368" t="s">
         <v>558</v>
@@ -35528,7 +35528,7 @@
         <v>32</v>
       </c>
       <c r="P369">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R369" t="s">
         <v>558</v>
@@ -35581,7 +35581,7 @@
         <v>31</v>
       </c>
       <c r="P370">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R370" t="s">
         <v>558</v>
@@ -35634,7 +35634,7 @@
         <v>33</v>
       </c>
       <c r="P371">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R371" t="s">
         <v>558</v>
@@ -35687,7 +35687,7 @@
         <v>32</v>
       </c>
       <c r="P372">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R372" t="s">
         <v>558</v>
@@ -35740,7 +35740,7 @@
         <v>31</v>
       </c>
       <c r="P373">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R373" t="s">
         <v>558</v>
@@ -35793,7 +35793,7 @@
         <v>33</v>
       </c>
       <c r="P374">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R374" t="s">
         <v>558</v>
@@ -35846,7 +35846,7 @@
         <v>32</v>
       </c>
       <c r="P375">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R375" t="s">
         <v>558</v>
@@ -35899,7 +35899,7 @@
         <v>31</v>
       </c>
       <c r="P376">
-        <v>0.11589158151298153</v>
+        <v>0.11589158151298157</v>
       </c>
       <c r="R376" t="s">
         <v>558</v>
@@ -36903,7 +36903,7 @@
         <v>17</v>
       </c>
       <c r="U392" t="s">
-        <v>559</v>
+        <v>790</v>
       </c>
       <c r="V392" t="s">
         <v>560</v>
@@ -36965,7 +36965,7 @@
         <v>17</v>
       </c>
       <c r="U393" t="s">
-        <v>790</v>
+        <v>559</v>
       </c>
       <c r="V393" t="s">
         <v>560</v>
@@ -37027,7 +37027,7 @@
         <v>17</v>
       </c>
       <c r="U394" t="s">
-        <v>790</v>
+        <v>559</v>
       </c>
       <c r="V394" t="s">
         <v>560</v>
@@ -37089,7 +37089,7 @@
         <v>17</v>
       </c>
       <c r="U395" t="s">
-        <v>559</v>
+        <v>790</v>
       </c>
       <c r="V395" t="s">
         <v>560</v>
@@ -37709,7 +37709,7 @@
         <v>17</v>
       </c>
       <c r="U405" t="s">
-        <v>790</v>
+        <v>559</v>
       </c>
       <c r="V405" t="s">
         <v>560</v>
@@ -37771,7 +37771,7 @@
         <v>17</v>
       </c>
       <c r="U406" t="s">
-        <v>559</v>
+        <v>790</v>
       </c>
       <c r="V406" t="s">
         <v>560</v>
@@ -49220,7 +49220,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DE60C4-D4D7-4212-B1AE-66955C23EB2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BF107C-67C3-42FA-A1B0-955C1C4832AE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
